--- a/outputs/daily/hr_rankings_2026-08-11.xlsx
+++ b/outputs/daily/hr_rankings_2026-08-11.xlsx
@@ -9771,27 +9771,27 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>691023</t>
+          <t>592626</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Jordan Walker</t>
+          <t>Joc Pederson</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>STL</t>
+          <t>TEX</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>LAA</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-08-11T23:45:00Z</t>
+          <t>2026-08-12T01:38:00Z</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -9801,26 +9801,26 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Cristopher Sánchez</t>
+          <t>Ryan Johnson</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>650911</t>
+          <t>696270</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L35" t="n">
-        <v>52.6</v>
+        <v>52.4</v>
       </c>
       <c r="M35" t="inlineStr">
         <is>
@@ -9838,22 +9838,22 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>55.6</v>
+        <v>49</v>
       </c>
       <c r="Q35" t="n">
-        <v>33.3</v>
+        <v>46.8</v>
       </c>
       <c r="R35" t="n">
-        <v>22.1</v>
+        <v>28.2</v>
       </c>
       <c r="S35" t="n">
-        <v>95.5</v>
+        <v>88.7</v>
       </c>
       <c r="T35" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="U35" t="n">
-        <v>51.9</v>
+        <v>22.8</v>
       </c>
       <c r="V35" t="inlineStr">
         <is>
@@ -9867,7 +9867,7 @@
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Y35" t="inlineStr">
@@ -9909,12 +9909,12 @@
       </c>
       <c r="AH35" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI35" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AJ35" t="inlineStr">
@@ -9924,119 +9924,119 @@
       </c>
       <c r="AK35" t="inlineStr">
         <is>
-          <t>Contact streak: 11/32 over last 7 games</t>
+          <t>Last 7 games: 3/20, 1 HR</t>
         </is>
       </c>
       <c r="AL35" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 7.2% barrel, 12.7 HR allowed</t>
+          <t>platoon edge; pitcher baseline 10.0% barrel, 10.3 HR allowed</t>
         </is>
       </c>
       <c r="AM35" t="inlineStr">
         <is>
-          <t>EV profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN35" t="inlineStr">
         <is>
-          <t>12.58</t>
+          <t>10.76</t>
         </is>
       </c>
       <c r="AO35" t="inlineStr">
         <is>
-          <t>48.32</t>
+          <t>48.3</t>
         </is>
       </c>
       <c r="AP35" t="inlineStr">
         <is>
-          <t>92.58</t>
+          <t>91.76</t>
         </is>
       </c>
       <c r="AQ35" t="inlineStr">
         <is>
-          <t>104.7741</t>
+          <t>102.0016</t>
         </is>
       </c>
       <c r="AR35" t="inlineStr">
         <is>
-          <t>0.4498</t>
+          <t>0.4378</t>
         </is>
       </c>
       <c r="AS35" t="inlineStr">
         <is>
-          <t>0.1942</t>
+          <t>0.1943</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr">
         <is>
-          <t>0.3319</t>
+          <t>0.3402</t>
         </is>
       </c>
       <c r="AU35" t="inlineStr">
         <is>
-          <t>78.87</t>
+          <t>72.39</t>
         </is>
       </c>
       <c r="AV35" t="inlineStr">
         <is>
-          <t>83.05</t>
+          <t>23.94</t>
         </is>
       </c>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>38.59</t>
+          <t>42.06</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>23.42</t>
+          <t>29.4</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr">
         <is>
-          <t>17.9</t>
+          <t>17.4</t>
         </is>
       </c>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>0.1708</t>
+          <t>0.2205</t>
         </is>
       </c>
       <c r="BA35" t="inlineStr">
         <is>
-          <t>7.17</t>
+          <t>9.97</t>
         </is>
       </c>
       <c r="BB35" t="inlineStr">
         <is>
-          <t>41.83</t>
+          <t>36.07</t>
         </is>
       </c>
       <c r="BC35" t="inlineStr">
         <is>
-          <t>89.28</t>
+          <t>87.26</t>
         </is>
       </c>
       <c r="BD35" t="inlineStr">
         <is>
-          <t>0.3569</t>
+          <t>0.4535</t>
         </is>
       </c>
       <c r="BE35" t="inlineStr">
         <is>
-          <t>0.1242</t>
+          <t>0.191</t>
         </is>
       </c>
       <c r="BF35" t="inlineStr">
         <is>
-          <t>16.97</t>
+          <t>32.55</t>
         </is>
       </c>
       <c r="BG35" t="inlineStr"/>
       <c r="BH35" t="inlineStr"/>
       <c r="BI35" t="inlineStr">
         <is>
-          <t>Busch Stadium</t>
+          <t>Angel Stadium</t>
         </is>
       </c>
       <c r="BJ35" t="inlineStr"/>
@@ -10047,27 +10047,27 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>592626</t>
+          <t>696100</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Joc Pederson</t>
+          <t>Hunter Goodman</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>TEX</t>
+          <t>COL</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>LAA</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-08-12T01:38:00Z</t>
+          <t>2026-08-12T01:40:00Z</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -10077,26 +10077,26 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>Ryan Johnson</t>
+          <t>Mitch Bratt</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>696270</t>
+          <t>683352</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L36" t="n">
-        <v>52.4</v>
+        <v>52.3</v>
       </c>
       <c r="M36" t="inlineStr">
         <is>
@@ -10114,22 +10114,22 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>49</v>
+        <v>59.4</v>
       </c>
       <c r="Q36" t="n">
-        <v>46.8</v>
+        <v>31.4</v>
       </c>
       <c r="R36" t="n">
         <v>28.2</v>
       </c>
       <c r="S36" t="n">
-        <v>88.7</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="T36" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="U36" t="n">
-        <v>22.8</v>
+        <v>25.3</v>
       </c>
       <c r="V36" t="inlineStr">
         <is>
@@ -10143,7 +10143,7 @@
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="Y36" t="inlineStr">
@@ -10168,7 +10168,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD36" t="inlineStr"/>
@@ -10185,12 +10185,12 @@
       </c>
       <c r="AH36" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI36" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ36" t="inlineStr">
@@ -10200,12 +10200,12 @@
       </c>
       <c r="AK36" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/20, 1 HR</t>
+          <t>Last 7 games: 4/24, 1 HR</t>
         </is>
       </c>
       <c r="AL36" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 10.0% barrel, 10.3 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.3% barrel, 4.0 HR allowed</t>
         </is>
       </c>
       <c r="AM36" t="inlineStr">
@@ -10215,104 +10215,104 @@
       </c>
       <c r="AN36" t="inlineStr">
         <is>
-          <t>10.76</t>
+          <t>15.56</t>
         </is>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
-          <t>48.3</t>
+          <t>46.2</t>
         </is>
       </c>
       <c r="AP36" t="inlineStr">
         <is>
-          <t>91.76</t>
+          <t>90.59</t>
         </is>
       </c>
       <c r="AQ36" t="inlineStr">
         <is>
-          <t>102.0016</t>
+          <t>102.7245</t>
         </is>
       </c>
       <c r="AR36" t="inlineStr">
         <is>
-          <t>0.4378</t>
+          <t>0.4637</t>
         </is>
       </c>
       <c r="AS36" t="inlineStr">
         <is>
-          <t>0.1943</t>
+          <t>0.2301</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr">
         <is>
-          <t>0.3402</t>
+          <t>0.3255</t>
         </is>
       </c>
       <c r="AU36" t="inlineStr">
         <is>
-          <t>72.39</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="AV36" t="inlineStr">
         <is>
-          <t>23.94</t>
+          <t>49.79</t>
         </is>
       </c>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>42.06</t>
+          <t>47.86</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>29.4</t>
+          <t>33.18</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr">
         <is>
-          <t>17.4</t>
+          <t>33.1</t>
         </is>
       </c>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>0.2205</t>
+          <t>0.2756</t>
         </is>
       </c>
       <c r="BA36" t="inlineStr">
         <is>
-          <t>9.97</t>
+          <t>7.3</t>
         </is>
       </c>
       <c r="BB36" t="inlineStr">
         <is>
-          <t>36.07</t>
+          <t>36.6</t>
         </is>
       </c>
       <c r="BC36" t="inlineStr">
         <is>
-          <t>87.26</t>
+          <t>87.7</t>
         </is>
       </c>
       <c r="BD36" t="inlineStr">
         <is>
-          <t>0.4535</t>
+          <t>0.356</t>
         </is>
       </c>
       <c r="BE36" t="inlineStr">
         <is>
-          <t>0.191</t>
+          <t>0.143</t>
         </is>
       </c>
       <c r="BF36" t="inlineStr">
         <is>
-          <t>32.55</t>
+          <t>32.9</t>
         </is>
       </c>
       <c r="BG36" t="inlineStr"/>
       <c r="BH36" t="inlineStr"/>
       <c r="BI36" t="inlineStr">
         <is>
-          <t>Angel Stadium</t>
+          <t>Chase Field</t>
         </is>
       </c>
       <c r="BJ36" t="inlineStr"/>
@@ -10323,27 +10323,27 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>696100</t>
+          <t>693307</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Hunter Goodman</t>
+          <t>Dillon Dingler</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>COL</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-08-12T01:40:00Z</t>
+          <t>2026-08-11T22:40:00Z</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -10353,26 +10353,26 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Mitch Bratt</t>
+          <t>Tanner Bibee</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>683352</t>
+          <t>676440</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L37" t="n">
-        <v>52.3</v>
+        <v>52.2</v>
       </c>
       <c r="M37" t="inlineStr">
         <is>
@@ -10386,26 +10386,26 @@
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P37" t="n">
-        <v>59.4</v>
+        <v>47.2</v>
       </c>
       <c r="Q37" t="n">
-        <v>31.4</v>
+        <v>45.3</v>
       </c>
       <c r="R37" t="n">
-        <v>28.2</v>
+        <v>27.6</v>
       </c>
       <c r="S37" t="n">
-        <v>90.40000000000001</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="T37" t="n">
-        <v>78</v>
+        <v>50</v>
       </c>
       <c r="U37" t="n">
-        <v>25.3</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="V37" t="inlineStr">
         <is>
@@ -10419,7 +10419,7 @@
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Y37" t="inlineStr">
@@ -10444,7 +10444,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD37" t="inlineStr"/>
@@ -10461,134 +10461,134 @@
       </c>
       <c r="AH37" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AI37" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>31</t>
         </is>
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/24, 1 HR</t>
+          <t>Hot streak: 3 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL37" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 7.3% barrel, 4.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.7% barrel, 24.2 HR allowed</t>
         </is>
       </c>
       <c r="AM37" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN37" t="inlineStr">
         <is>
-          <t>15.56</t>
+          <t>10.74</t>
         </is>
       </c>
       <c r="AO37" t="inlineStr">
         <is>
-          <t>46.2</t>
+          <t>44.72</t>
         </is>
       </c>
       <c r="AP37" t="inlineStr">
         <is>
-          <t>90.59</t>
+          <t>89.3</t>
         </is>
       </c>
       <c r="AQ37" t="inlineStr">
         <is>
-          <t>102.7245</t>
+          <t>100.8945</t>
         </is>
       </c>
       <c r="AR37" t="inlineStr">
         <is>
-          <t>0.4637</t>
+          <t>0.5016</t>
         </is>
       </c>
       <c r="AS37" t="inlineStr">
         <is>
-          <t>0.2301</t>
+          <t>0.2151</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr">
         <is>
-          <t>0.3255</t>
+          <t>0.3664</t>
         </is>
       </c>
       <c r="AU37" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>71.77</t>
         </is>
       </c>
       <c r="AV37" t="inlineStr">
         <is>
-          <t>49.79</t>
+          <t>15.48</t>
         </is>
       </c>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>47.86</t>
+          <t>40.66</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>33.18</t>
+          <t>28.15</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr">
         <is>
-          <t>33.1</t>
+          <t>22.1</t>
         </is>
       </c>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>0.2756</t>
+          <t>0.2212</t>
         </is>
       </c>
       <c r="BA37" t="inlineStr">
         <is>
-          <t>7.3</t>
+          <t>8.66</t>
         </is>
       </c>
       <c r="BB37" t="inlineStr">
         <is>
-          <t>36.6</t>
+          <t>38.7</t>
         </is>
       </c>
       <c r="BC37" t="inlineStr">
         <is>
-          <t>87.7</t>
+          <t>89.13</t>
         </is>
       </c>
       <c r="BD37" t="inlineStr">
         <is>
-          <t>0.356</t>
+          <t>0.4172</t>
         </is>
       </c>
       <c r="BE37" t="inlineStr">
         <is>
-          <t>0.143</t>
+          <t>0.1702</t>
         </is>
       </c>
       <c r="BF37" t="inlineStr">
         <is>
-          <t>32.9</t>
+          <t>27.41</t>
         </is>
       </c>
       <c r="BG37" t="inlineStr"/>
       <c r="BH37" t="inlineStr"/>
       <c r="BI37" t="inlineStr">
         <is>
-          <t>Chase Field</t>
+          <t>Comerica Park</t>
         </is>
       </c>
       <c r="BJ37" t="inlineStr"/>
@@ -10599,27 +10599,27 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>693307</t>
+          <t>691023</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Dillon Dingler</t>
+          <t>Jordan Walker</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>STL</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-08-11T22:40:00Z</t>
+          <t>2026-08-11T23:45:00Z</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -10634,17 +10634,17 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>Tanner Bibee</t>
+          <t>Cristopher Sánchez</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>676440</t>
+          <t>650911</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L38" t="n">
@@ -10662,26 +10662,26 @@
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Hot Hitter/Streak</t>
+          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P38" t="n">
-        <v>47.2</v>
+        <v>55.6</v>
       </c>
       <c r="Q38" t="n">
-        <v>45.3</v>
+        <v>33.3</v>
       </c>
       <c r="R38" t="n">
-        <v>27.6</v>
+        <v>22.1</v>
       </c>
       <c r="S38" t="n">
         <v>92.09999999999999</v>
       </c>
       <c r="T38" t="n">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="U38" t="n">
-        <v>85.40000000000001</v>
+        <v>51.9</v>
       </c>
       <c r="V38" t="inlineStr">
         <is>
@@ -10737,134 +10737,134 @@
       </c>
       <c r="AH38" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AI38" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>32</t>
         </is>
       </c>
       <c r="AJ38" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK38" t="inlineStr">
         <is>
-          <t>Hot streak: 3 HR in last 7 games</t>
+          <t>Contact streak: 11/32 over last 7 games</t>
         </is>
       </c>
       <c r="AL38" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.7% barrel, 24.2 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.2% barrel, 12.7 HR allowed</t>
         </is>
       </c>
       <c r="AM38" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>EV profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN38" t="inlineStr">
         <is>
-          <t>10.74</t>
+          <t>12.58</t>
         </is>
       </c>
       <c r="AO38" t="inlineStr">
         <is>
-          <t>44.72</t>
+          <t>48.32</t>
         </is>
       </c>
       <c r="AP38" t="inlineStr">
         <is>
-          <t>89.3</t>
+          <t>92.58</t>
         </is>
       </c>
       <c r="AQ38" t="inlineStr">
         <is>
-          <t>100.8945</t>
+          <t>104.7741</t>
         </is>
       </c>
       <c r="AR38" t="inlineStr">
         <is>
-          <t>0.5016</t>
+          <t>0.4498</t>
         </is>
       </c>
       <c r="AS38" t="inlineStr">
         <is>
-          <t>0.2151</t>
+          <t>0.1942</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr">
         <is>
-          <t>0.3664</t>
+          <t>0.3319</t>
         </is>
       </c>
       <c r="AU38" t="inlineStr">
         <is>
-          <t>71.77</t>
+          <t>78.87</t>
         </is>
       </c>
       <c r="AV38" t="inlineStr">
         <is>
-          <t>15.48</t>
+          <t>83.05</t>
         </is>
       </c>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>40.66</t>
+          <t>38.59</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>28.15</t>
+          <t>23.42</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr">
         <is>
-          <t>22.1</t>
+          <t>17.9</t>
         </is>
       </c>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>0.2212</t>
+          <t>0.1708</t>
         </is>
       </c>
       <c r="BA38" t="inlineStr">
         <is>
-          <t>8.66</t>
+          <t>7.17</t>
         </is>
       </c>
       <c r="BB38" t="inlineStr">
         <is>
-          <t>38.7</t>
+          <t>41.83</t>
         </is>
       </c>
       <c r="BC38" t="inlineStr">
         <is>
-          <t>89.13</t>
+          <t>89.28</t>
         </is>
       </c>
       <c r="BD38" t="inlineStr">
         <is>
-          <t>0.4172</t>
+          <t>0.3569</t>
         </is>
       </c>
       <c r="BE38" t="inlineStr">
         <is>
-          <t>0.1702</t>
+          <t>0.1242</t>
         </is>
       </c>
       <c r="BF38" t="inlineStr">
         <is>
-          <t>27.41</t>
+          <t>16.97</t>
         </is>
       </c>
       <c r="BG38" t="inlineStr"/>
       <c r="BH38" t="inlineStr"/>
       <c r="BI38" t="inlineStr">
         <is>
-          <t>Comerica Park</t>
+          <t>Busch Stadium</t>
         </is>
       </c>
       <c r="BJ38" t="inlineStr"/>
@@ -26187,27 +26187,27 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>663616</t>
+          <t>671056</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Trevor Larnach</t>
+          <t>Ivan Herrera</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>STL</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>BAL</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>2026-08-11T23:40:00Z</t>
+          <t>2026-08-11T23:45:00Z</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
@@ -26217,26 +26217,26 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>Brandon Young</t>
+          <t>Cristopher Sánchez</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>687064</t>
+          <t>650911</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L95" t="n">
-        <v>46</v>
+        <v>46.1</v>
       </c>
       <c r="M95" t="inlineStr">
         <is>
@@ -26254,22 +26254,22 @@
         </is>
       </c>
       <c r="P95" t="n">
-        <v>30.3</v>
+        <v>34.9</v>
       </c>
       <c r="Q95" t="n">
-        <v>41.7</v>
+        <v>33.3</v>
       </c>
       <c r="R95" t="n">
-        <v>27.1</v>
+        <v>22.1</v>
       </c>
       <c r="S95" t="n">
-        <v>88.7</v>
+        <v>95.5</v>
       </c>
       <c r="T95" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="U95" t="n">
-        <v>45.9</v>
+        <v>58.4</v>
       </c>
       <c r="V95" t="inlineStr">
         <is>
@@ -26283,7 +26283,7 @@
       </c>
       <c r="X95" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Y95" t="inlineStr">
@@ -26325,27 +26325,27 @@
       </c>
       <c r="AH95" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AI95" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>31</t>
         </is>
       </c>
       <c r="AJ95" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK95" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Contact streak: 12/31 over last 7 games</t>
         </is>
       </c>
       <c r="AL95" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 7.5% barrel, 12.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.2% barrel, 12.7 HR allowed</t>
         </is>
       </c>
       <c r="AM95" t="inlineStr">
@@ -26355,104 +26355,104 @@
       </c>
       <c r="AN95" t="inlineStr">
         <is>
-          <t>7.55</t>
+          <t>7.25</t>
         </is>
       </c>
       <c r="AO95" t="inlineStr">
         <is>
-          <t>38.77</t>
+          <t>43.22</t>
         </is>
       </c>
       <c r="AP95" t="inlineStr">
         <is>
-          <t>88.38</t>
+          <t>90.08</t>
         </is>
       </c>
       <c r="AQ95" t="inlineStr">
         <is>
-          <t>99.5508</t>
+          <t>101.478</t>
         </is>
       </c>
       <c r="AR95" t="inlineStr">
         <is>
-          <t>0.4016</t>
+          <t>0.4107</t>
         </is>
       </c>
       <c r="AS95" t="inlineStr">
         <is>
-          <t>0.1474</t>
+          <t>0.1541</t>
         </is>
       </c>
       <c r="AT95" t="inlineStr">
         <is>
-          <t>0.3278</t>
+          <t>0.3421</t>
         </is>
       </c>
       <c r="AU95" t="inlineStr">
         <is>
-          <t>72.03</t>
+          <t>73.95</t>
         </is>
       </c>
       <c r="AV95" t="inlineStr">
         <is>
-          <t>21.85</t>
+          <t>43.77</t>
         </is>
       </c>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>42.2</t>
+          <t>37.8</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>24.54</t>
+          <t>18.89</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr">
         <is>
-          <t>12.1</t>
+          <t>14.8</t>
         </is>
       </c>
       <c r="AZ95" t="inlineStr">
         <is>
-          <t>0.1624</t>
+          <t>0.1548</t>
         </is>
       </c>
       <c r="BA95" t="inlineStr">
         <is>
-          <t>7.54</t>
+          <t>7.17</t>
         </is>
       </c>
       <c r="BB95" t="inlineStr">
         <is>
-          <t>41.29</t>
+          <t>41.83</t>
         </is>
       </c>
       <c r="BC95" t="inlineStr">
         <is>
-          <t>89.4</t>
+          <t>89.28</t>
         </is>
       </c>
       <c r="BD95" t="inlineStr">
         <is>
-          <t>0.4152</t>
+          <t>0.3569</t>
         </is>
       </c>
       <c r="BE95" t="inlineStr">
         <is>
-          <t>0.163</t>
+          <t>0.1242</t>
         </is>
       </c>
       <c r="BF95" t="inlineStr">
         <is>
-          <t>27.57</t>
+          <t>16.97</t>
         </is>
       </c>
       <c r="BG95" t="inlineStr"/>
       <c r="BH95" t="inlineStr"/>
       <c r="BI95" t="inlineStr">
         <is>
-          <t>Target Field</t>
+          <t>Busch Stadium</t>
         </is>
       </c>
       <c r="BJ95" t="inlineStr"/>
@@ -26463,12 +26463,12 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>680777</t>
+          <t>663616</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Ryan Jeffers</t>
+          <t>Trevor Larnach</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -26493,7 +26493,7 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
@@ -26526,11 +26526,11 @@
       </c>
       <c r="O96" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P96" t="n">
-        <v>40.4</v>
+        <v>30.3</v>
       </c>
       <c r="Q96" t="n">
         <v>41.7</v>
@@ -26539,13 +26539,13 @@
         <v>27.1</v>
       </c>
       <c r="S96" t="n">
-        <v>95.5</v>
+        <v>88.7</v>
       </c>
       <c r="T96" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U96" t="n">
-        <v>14.6</v>
+        <v>45.9</v>
       </c>
       <c r="V96" t="inlineStr">
         <is>
@@ -26559,7 +26559,7 @@
       </c>
       <c r="X96" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Y96" t="inlineStr">
@@ -26601,27 +26601,27 @@
       </c>
       <c r="AH96" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI96" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AJ96" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK96" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/23, 0 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL96" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 7.5% barrel, 12.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.5% barrel, 12.0 HR allowed</t>
         </is>
       </c>
       <c r="AM96" t="inlineStr">
@@ -26631,67 +26631,67 @@
       </c>
       <c r="AN96" t="inlineStr">
         <is>
-          <t>9.66</t>
+          <t>7.55</t>
         </is>
       </c>
       <c r="AO96" t="inlineStr">
         <is>
-          <t>41.12</t>
+          <t>38.77</t>
         </is>
       </c>
       <c r="AP96" t="inlineStr">
         <is>
-          <t>89.37</t>
+          <t>88.38</t>
         </is>
       </c>
       <c r="AQ96" t="inlineStr">
         <is>
-          <t>100.9724</t>
+          <t>99.5508</t>
         </is>
       </c>
       <c r="AR96" t="inlineStr">
         <is>
-          <t>0.4378</t>
+          <t>0.4016</t>
         </is>
       </c>
       <c r="AS96" t="inlineStr">
         <is>
-          <t>0.1829</t>
+          <t>0.1474</t>
         </is>
       </c>
       <c r="AT96" t="inlineStr">
         <is>
-          <t>0.3537</t>
+          <t>0.3278</t>
         </is>
       </c>
       <c r="AU96" t="inlineStr">
         <is>
-          <t>72.93</t>
+          <t>72.03</t>
         </is>
       </c>
       <c r="AV96" t="inlineStr">
         <is>
-          <t>35.49</t>
+          <t>21.85</t>
         </is>
       </c>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>36.83</t>
+          <t>42.2</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>27.47</t>
+          <t>24.54</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr">
         <is>
-          <t>9.7</t>
+          <t>12.1</t>
         </is>
       </c>
       <c r="AZ96" t="inlineStr">
         <is>
-          <t>0.1912</t>
+          <t>0.1624</t>
         </is>
       </c>
       <c r="BA96" t="inlineStr">
@@ -26739,27 +26739,27 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>800050</t>
+          <t>680777</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Chase DeLauter</t>
+          <t>Ryan Jeffers</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>BAL</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>2026-08-11T22:40:00Z</t>
+          <t>2026-08-11T23:40:00Z</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
@@ -26774,12 +26774,12 @@
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>Drew Anderson</t>
+          <t>Brandon Young</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>623454</t>
+          <t>687064</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
@@ -26788,7 +26788,7 @@
         </is>
       </c>
       <c r="L97" t="n">
-        <v>45.9</v>
+        <v>46</v>
       </c>
       <c r="M97" t="inlineStr">
         <is>
@@ -26802,26 +26802,26 @@
       </c>
       <c r="O97" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Projected Lineup, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P97" t="n">
-        <v>34.9</v>
+        <v>40.4</v>
       </c>
       <c r="Q97" t="n">
-        <v>34.6</v>
+        <v>41.7</v>
       </c>
       <c r="R97" t="n">
-        <v>27.6</v>
+        <v>27.1</v>
       </c>
       <c r="S97" t="n">
         <v>95.5</v>
       </c>
       <c r="T97" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U97" t="n">
-        <v>26.4</v>
+        <v>14.6</v>
       </c>
       <c r="V97" t="inlineStr">
         <is>
@@ -26860,7 +26860,7 @@
       </c>
       <c r="AC97" t="inlineStr">
         <is>
-          <t>H:2026 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD97" t="inlineStr"/>
@@ -26877,12 +26877,12 @@
       </c>
       <c r="AH97" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI97" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AJ97" t="inlineStr">
@@ -26892,12 +26892,12 @@
       </c>
       <c r="AK97" t="inlineStr">
         <is>
-          <t>Last 7 games: 8/27, 0 HR</t>
+          <t>Last 7 games: 5/23, 0 HR</t>
         </is>
       </c>
       <c r="AL97" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 7.7% barrel, 9.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 7.5% barrel, 12.0 HR allowed</t>
         </is>
       </c>
       <c r="AM97" t="inlineStr">
@@ -26907,104 +26907,104 @@
       </c>
       <c r="AN97" t="inlineStr">
         <is>
-          <t>6.3</t>
+          <t>9.66</t>
         </is>
       </c>
       <c r="AO97" t="inlineStr">
         <is>
-          <t>46.1</t>
+          <t>41.12</t>
         </is>
       </c>
       <c r="AP97" t="inlineStr">
         <is>
-          <t>91.2</t>
+          <t>89.37</t>
         </is>
       </c>
       <c r="AQ97" t="inlineStr">
         <is>
-          <t>101.5411</t>
+          <t>100.9724</t>
         </is>
       </c>
       <c r="AR97" t="inlineStr">
         <is>
-          <t>0.426</t>
+          <t>0.4378</t>
         </is>
       </c>
       <c r="AS97" t="inlineStr">
         <is>
-          <t>0.152</t>
+          <t>0.1829</t>
         </is>
       </c>
       <c r="AT97" t="inlineStr">
         <is>
-          <t>0.346</t>
+          <t>0.3537</t>
         </is>
       </c>
       <c r="AU97" t="inlineStr">
         <is>
-          <t>71.4</t>
+          <t>72.93</t>
         </is>
       </c>
       <c r="AV97" t="inlineStr">
         <is>
-          <t>17.9</t>
+          <t>35.49</t>
         </is>
       </c>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>38.1</t>
+          <t>36.83</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>19.1</t>
+          <t>27.47</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr">
         <is>
-          <t>12.0</t>
+          <t>9.7</t>
         </is>
       </c>
       <c r="AZ97" t="inlineStr">
         <is>
-          <t>0.156</t>
+          <t>0.1912</t>
         </is>
       </c>
       <c r="BA97" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>7.54</t>
         </is>
       </c>
       <c r="BB97" t="inlineStr">
         <is>
-          <t>39.0</t>
+          <t>41.29</t>
         </is>
       </c>
       <c r="BC97" t="inlineStr">
         <is>
-          <t>90.3</t>
+          <t>89.4</t>
         </is>
       </c>
       <c r="BD97" t="inlineStr">
         <is>
-          <t>0.343</t>
+          <t>0.4152</t>
         </is>
       </c>
       <c r="BE97" t="inlineStr">
         <is>
-          <t>0.131</t>
+          <t>0.163</t>
         </is>
       </c>
       <c r="BF97" t="inlineStr">
         <is>
-          <t>23.6</t>
+          <t>27.57</t>
         </is>
       </c>
       <c r="BG97" t="inlineStr"/>
       <c r="BH97" t="inlineStr"/>
       <c r="BI97" t="inlineStr">
         <is>
-          <t>Comerica Park</t>
+          <t>Target Field</t>
         </is>
       </c>
       <c r="BJ97" t="inlineStr"/>
@@ -27015,27 +27015,27 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>806146</t>
+          <t>800050</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>George Lombard</t>
+          <t>Chase DeLauter</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>NYY</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>2026-08-11T23:05:00Z</t>
+          <t>2026-08-11T22:40:00Z</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
@@ -27045,17 +27045,17 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>Bryan Woo</t>
+          <t>Drew Anderson</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>693433</t>
+          <t>623454</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
@@ -27064,7 +27064,7 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>45.6</v>
+        <v>45.9</v>
       </c>
       <c r="M98" t="inlineStr">
         <is>
@@ -27078,26 +27078,26 @@
       </c>
       <c r="O98" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel</t>
+          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P98" t="n">
-        <v>42.5</v>
+        <v>34.9</v>
       </c>
       <c r="Q98" t="n">
-        <v>41.2</v>
+        <v>34.6</v>
       </c>
       <c r="R98" t="n">
-        <v>38.2</v>
+        <v>27.6</v>
       </c>
       <c r="S98" t="n">
-        <v>59.8</v>
+        <v>95.5</v>
       </c>
       <c r="T98" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U98" t="n">
-        <v>62.8</v>
+        <v>26.4</v>
       </c>
       <c r="V98" t="inlineStr">
         <is>
@@ -27111,7 +27111,7 @@
       </c>
       <c r="X98" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Y98" t="inlineStr">
@@ -27136,7 +27136,7 @@
       </c>
       <c r="AC98" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026 P:2026</t>
         </is>
       </c>
       <c r="AD98" t="inlineStr"/>
@@ -27148,32 +27148,32 @@
       </c>
       <c r="AG98" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AH98" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AI98" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ98" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK98" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 5 games</t>
+          <t>Last 7 games: 8/27, 0 HR</t>
         </is>
       </c>
       <c r="AL98" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 7.6% barrel, 16.9 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.7% barrel, 9.0 HR allowed</t>
         </is>
       </c>
       <c r="AM98" t="inlineStr">
@@ -27183,104 +27183,104 @@
       </c>
       <c r="AN98" t="inlineStr">
         <is>
-          <t>16.7</t>
+          <t>6.3</t>
         </is>
       </c>
       <c r="AO98" t="inlineStr">
         <is>
-          <t>41.7</t>
+          <t>46.1</t>
         </is>
       </c>
       <c r="AP98" t="inlineStr">
         <is>
-          <t>84.7</t>
+          <t>91.2</t>
         </is>
       </c>
       <c r="AQ98" t="inlineStr">
         <is>
-          <t>98.8973</t>
+          <t>101.5411</t>
         </is>
       </c>
       <c r="AR98" t="inlineStr">
         <is>
-          <t>0.435</t>
+          <t>0.426</t>
         </is>
       </c>
       <c r="AS98" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>0.152</t>
         </is>
       </c>
       <c r="AT98" t="inlineStr">
         <is>
-          <t>0.359</t>
+          <t>0.346</t>
         </is>
       </c>
       <c r="AU98" t="inlineStr">
         <is>
-          <t>70.9</t>
+          <t>71.4</t>
         </is>
       </c>
       <c r="AV98" t="inlineStr">
         <is>
-          <t>11.8</t>
+          <t>17.9</t>
         </is>
       </c>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>33.3</t>
+          <t>38.1</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>19.1</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="AZ98" t="inlineStr">
         <is>
-          <t>0.353</t>
+          <t>0.156</t>
         </is>
       </c>
       <c r="BA98" t="inlineStr">
         <is>
-          <t>7.56</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="BB98" t="inlineStr">
         <is>
-          <t>42.43</t>
+          <t>39.0</t>
         </is>
       </c>
       <c r="BC98" t="inlineStr">
         <is>
-          <t>89.38</t>
+          <t>90.3</t>
         </is>
       </c>
       <c r="BD98" t="inlineStr">
         <is>
-          <t>0.3828</t>
+          <t>0.343</t>
         </is>
       </c>
       <c r="BE98" t="inlineStr">
         <is>
-          <t>0.1499</t>
+          <t>0.131</t>
         </is>
       </c>
       <c r="BF98" t="inlineStr">
         <is>
-          <t>28.27</t>
+          <t>23.6</t>
         </is>
       </c>
       <c r="BG98" t="inlineStr"/>
       <c r="BH98" t="inlineStr"/>
       <c r="BI98" t="inlineStr">
         <is>
-          <t>Yankee Stadium</t>
+          <t>Comerica Park</t>
         </is>
       </c>
       <c r="BJ98" t="inlineStr"/>
@@ -27291,27 +27291,27 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>671056</t>
+          <t>806146</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Ivan Herrera</t>
+          <t>George Lombard</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>STL</t>
+          <t>NYY</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>2026-08-11T23:45:00Z</t>
+          <t>2026-08-11T23:05:00Z</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
@@ -27321,22 +27321,22 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>Cristopher Sánchez</t>
+          <t>Bryan Woo</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>650911</t>
+          <t>693433</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L99" t="n">
@@ -27354,26 +27354,26 @@
       </c>
       <c r="O99" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Projected Lineup, Strong Barrel</t>
         </is>
       </c>
       <c r="P99" t="n">
-        <v>34.9</v>
+        <v>42.5</v>
       </c>
       <c r="Q99" t="n">
-        <v>33.3</v>
+        <v>41.2</v>
       </c>
       <c r="R99" t="n">
-        <v>22.1</v>
+        <v>38.2</v>
       </c>
       <c r="S99" t="n">
-        <v>92.09999999999999</v>
+        <v>59.8</v>
       </c>
       <c r="T99" t="n">
-        <v>78</v>
+        <v>50</v>
       </c>
       <c r="U99" t="n">
-        <v>58.4</v>
+        <v>62.8</v>
       </c>
       <c r="V99" t="inlineStr">
         <is>
@@ -27387,7 +27387,7 @@
       </c>
       <c r="X99" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="Y99" t="inlineStr">
@@ -27412,7 +27412,7 @@
       </c>
       <c r="AC99" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AD99" t="inlineStr"/>
@@ -27424,32 +27424,32 @@
       </c>
       <c r="AG99" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AH99" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI99" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>17</t>
         </is>
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK99" t="inlineStr">
         <is>
-          <t>Contact streak: 12/31 over last 7 games</t>
+          <t>Hot streak: 2 HR in last 5 games</t>
         </is>
       </c>
       <c r="AL99" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 7.2% barrel, 12.7 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 7.6% barrel, 16.9 HR allowed</t>
         </is>
       </c>
       <c r="AM99" t="inlineStr">
@@ -27459,104 +27459,104 @@
       </c>
       <c r="AN99" t="inlineStr">
         <is>
-          <t>7.25</t>
+          <t>16.7</t>
         </is>
       </c>
       <c r="AO99" t="inlineStr">
         <is>
-          <t>43.22</t>
+          <t>41.7</t>
         </is>
       </c>
       <c r="AP99" t="inlineStr">
         <is>
-          <t>90.08</t>
+          <t>84.7</t>
         </is>
       </c>
       <c r="AQ99" t="inlineStr">
         <is>
-          <t>101.478</t>
+          <t>98.8973</t>
         </is>
       </c>
       <c r="AR99" t="inlineStr">
         <is>
-          <t>0.4107</t>
+          <t>0.435</t>
         </is>
       </c>
       <c r="AS99" t="inlineStr">
         <is>
-          <t>0.1541</t>
+          <t>0.17</t>
         </is>
       </c>
       <c r="AT99" t="inlineStr">
         <is>
-          <t>0.3421</t>
+          <t>0.359</t>
         </is>
       </c>
       <c r="AU99" t="inlineStr">
         <is>
-          <t>73.95</t>
+          <t>70.9</t>
         </is>
       </c>
       <c r="AV99" t="inlineStr">
         <is>
-          <t>43.77</t>
+          <t>11.8</t>
         </is>
       </c>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>37.8</t>
+          <t>33.3</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>18.89</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr">
         <is>
-          <t>14.8</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="AZ99" t="inlineStr">
         <is>
-          <t>0.1548</t>
+          <t>0.353</t>
         </is>
       </c>
       <c r="BA99" t="inlineStr">
         <is>
-          <t>7.17</t>
+          <t>7.56</t>
         </is>
       </c>
       <c r="BB99" t="inlineStr">
         <is>
-          <t>41.83</t>
+          <t>42.43</t>
         </is>
       </c>
       <c r="BC99" t="inlineStr">
         <is>
-          <t>89.28</t>
+          <t>89.38</t>
         </is>
       </c>
       <c r="BD99" t="inlineStr">
         <is>
-          <t>0.3569</t>
+          <t>0.3828</t>
         </is>
       </c>
       <c r="BE99" t="inlineStr">
         <is>
-          <t>0.1242</t>
+          <t>0.1499</t>
         </is>
       </c>
       <c r="BF99" t="inlineStr">
         <is>
-          <t>16.97</t>
+          <t>28.27</t>
         </is>
       </c>
       <c r="BG99" t="inlineStr"/>
       <c r="BH99" t="inlineStr"/>
       <c r="BI99" t="inlineStr">
         <is>
-          <t>Busch Stadium</t>
+          <t>Yankee Stadium</t>
         </is>
       </c>
       <c r="BJ99" t="inlineStr"/>
